--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487014_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487014_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8999</v>
+        <v>12.4081</v>
       </c>
       <c r="E2" t="n">
-        <v>8.780799999999999</v>
+        <v>9.6448</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1191</v>
+        <v>2.7633</v>
       </c>
       <c r="G2" t="n">
         <v>13.7787</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4334</v>
+        <v>0.9416</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7905</v>
+        <v>0.0735</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2238</v>
+        <v>0.8681</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0572</v>
+        <v>6.5474</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7932</v>
+        <v>4.4019</v>
       </c>
       <c r="F3" t="n">
-        <v>2.264</v>
+        <v>2.1454</v>
       </c>
       <c r="G3" t="n">
         <v>4.4474</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3429</v>
+        <v>0.8331</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3408</v>
+        <v>-0.0505</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0021</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.2402</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3092</v>
+        <v>5.8704</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5447</v>
+        <v>6.6542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7645</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6181</v>
+        <v>3.8765</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9337</v>
+        <v>3.7922</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6843</v>
+        <v>0.0843</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5224</v>
+        <v>5.8016</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6542</v>
+        <v>3.8153</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8682</v>
+        <v>1.9863</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9044</v>
+        <v>-1.9251</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7204</v>
+        <v>-0.0231</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1839</v>
+        <v>-1.902</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7384</v>
+        <v>0.9056</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3016</v>
+        <v>0.0231</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4368</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7207</v>
+        <v>-0.3491</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7207</v>
+        <v>0.8295</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.6324</v>
+        <v>5.3447</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2087</v>
+        <v>4.6692</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5763</v>
+        <v>0.6755</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8765</v>
+        <v>2.6181</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7922</v>
+        <v>1.9337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0843</v>
+        <v>0.6843</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8016</v>
+        <v>3.5224</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8153</v>
+        <v>2.6542</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9863</v>
+        <v>0.8682</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9251</v>
+        <v>-0.9044</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0231</v>
+        <v>-0.7204</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.902</v>
+        <v>-0.1839</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6676</v>
+        <v>0.7739</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4225</v>
+        <v>0.426</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0901</v>
+        <v>0.3479</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3491</v>
+        <v>0.7207</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8295</v>
+        <v>0.7207</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1195</v>
+        <v>2.1006</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4773</v>
+        <v>2.4585</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3578</v>
@@ -922,10 +922,10 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2083</v>
+        <v>1.1895</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4333</v>
+        <v>0.4144</v>
       </c>
       <c r="U6" t="n">
         <v>0.775</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5966</v>
+        <v>1.3874</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3336</v>
+        <v>1.1243</v>
       </c>
       <c r="F7" t="n">
         <v>0.263</v>
@@ -1000,10 +1000,10 @@
         <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.5463</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5656</v>
+        <v>0.3564</v>
       </c>
       <c r="U7" t="n">
         <v>0.1899</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3851</v>
+        <v>1.2474</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5037</v>
+        <v>0.1511</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8888</v>
+        <v>1.0963</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0597</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2801</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7246</v>
+        <v>-0.0698</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4445</v>
+        <v>0.652</v>
       </c>
       <c r="V8" t="n">
         <v>0.1088</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0463</v>
+        <v>-0.3268</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0993</v>
+        <v>-0.4131</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1456</v>
+        <v>0.0864</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0881</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5184</v>
+        <v>0.1453</v>
       </c>
       <c r="T9" t="n">
-        <v>0.368</v>
+        <v>0.0542</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1504</v>
+        <v>0.0911</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6213</v>
+        <v>-1.8702</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0154</v>
+        <v>-0.5311</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.606</v>
+        <v>-1.3392</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9851</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6281</v>
+        <v>0.123</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.527</v>
+        <v>-0.0427</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1011</v>
+        <v>0.1657</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4189</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.335</v>
+        <v>-2.2529</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5459</v>
+        <v>-1.8699</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2109</v>
+        <v>-0.383</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.02</v>
+        <v>-2.1378</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2805</v>
+        <v>-0.0327</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7395</v>
+        <v>-2.1051</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4184</v>
+        <v>-1.707</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.5364</v>
+        <v>0.2141</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.882</v>
+        <v>-1.9212</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6017</v>
+        <v>-0.4308</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2559</v>
+        <v>-0.2468</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8575</v>
+        <v>-0.1839</v>
       </c>
       <c r="P11" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9222</v>
+        <v>-0.1628</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9912</v>
+        <v>0.1996</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3614</v>
+        <v>-2.7395</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5634</v>
+        <v>-3.8912</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.798</v>
+        <v>1.1517</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1378</v>
+        <v>-4.02</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0327</v>
+        <v>-2.2805</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1051</v>
+        <v>-1.7395</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.707</v>
+        <v>-3.4184</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2141</v>
+        <v>-2.5364</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9212</v>
+        <v>-0.882</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4308</v>
+        <v>-0.6017</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2468</v>
+        <v>0.2559</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1839</v>
+        <v>-0.8575</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0717</v>
+        <v>0.6645</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8563</v>
+        <v>-0.2674</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2153</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.7285</v>
+        <v>27.7166</v>
       </c>
       <c r="E13" t="n">
-        <v>21.4106</v>
+        <v>22.3987</v>
       </c>
       <c r="F13" t="n">
         <v>5.3178</v>
@@ -1465,16 +1465,16 @@
         <v>-5.1334</v>
       </c>
       <c r="R13" t="n">
-        <v>9.240399999999999</v>
+        <v>9.240400000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7536</v>
+        <v>6.741800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2338000000000002</v>
+        <v>0.7543999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>5.987400000000001</v>
+        <v>5.987500000000002</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8769</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3118</v>
+        <v>1.521</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3124</v>
+        <v>2.5216</v>
       </c>
       <c r="F14" t="n">
         <v>-1.0006</v>
@@ -1546,10 +1546,10 @@
         <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4107</v>
+        <v>-0.2015</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9222</v>
+        <v>-0.713</v>
       </c>
       <c r="U14" t="n">
         <v>0.5115</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.063</v>
+        <v>0.9741</v>
       </c>
       <c r="E15" t="n">
         <v>3.0586</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9956</v>
+        <v>-2.0846</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0921</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5513</v>
+        <v>-0.6402</v>
       </c>
       <c r="T15" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1347</v>
+        <v>0.0457</v>
       </c>
       <c r="V15" t="n">
         <v>2.117</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3171</v>
+        <v>-0.882</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1933</v>
+        <v>-1.4025</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8762</v>
+        <v>0.5205</v>
       </c>
       <c r="G16" t="n">
         <v>-1.223</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2898</v>
+        <v>-0.2751</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2249</v>
+        <v>-0.4341</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5147</v>
+        <v>0.159</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5755</v>
+        <v>-0.9043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2413</v>
+        <v>0.7643</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8169</v>
+        <v>-1.6687</v>
       </c>
       <c r="G17" t="n">
         <v>1.0997</v>
@@ -1780,13 +1780,13 @@
         <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4781</v>
+        <v>-0.8068</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1857</v>
+        <v>-0.6627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2924</v>
+        <v>-0.1442</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.374</v>
+        <v>-2.7454</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8337</v>
+        <v>-0.9383</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5403</v>
+        <v>-1.8071</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9986</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2755</v>
+        <v>-0.0959</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4883</v>
+        <v>-0.5929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7639</v>
+        <v>0.4971</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2402</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5132</v>
+        <v>-3.8334</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1973</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7106</v>
+        <v>-3.0043</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.2229</v>
+        <v>-2.9089</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9917</v>
+        <v>-0.2436</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2312</v>
+        <v>-2.6653</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1201</v>
+        <v>0.4578</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8439</v>
+        <v>1.6157</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7238</v>
+        <v>-1.1579</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.343</v>
+        <v>-3.3667</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.8356</v>
+        <v>-1.8593</v>
       </c>
       <c r="O19" t="n">
         <v>-1.5074</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3643</v>
+        <v>-0.7458</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.9378</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4416</v>
+        <v>0.1919</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4579</v>
+        <v>-0.5893</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4579</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2065</v>
+        <v>-3.9842</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1429</v>
+        <v>-0.5562</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0636</v>
+        <v>-3.428</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9089</v>
+        <v>-0.9202</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2436</v>
+        <v>-1.3363</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6653</v>
+        <v>0.4161</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4578</v>
+        <v>0.8494</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6157</v>
+        <v>0.6916</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1579</v>
+        <v>0.1579</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3667</v>
+        <v>-1.7696</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8593</v>
+        <v>-2.0279</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5074</v>
+        <v>0.2582</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4107</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1189</v>
+        <v>-0.7313</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2516</v>
+        <v>-0.2249</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1326</v>
+        <v>-0.5064</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5893</v>
+        <v>0.1314</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>1.8993</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2402</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3103</v>
+        <v>-4.2455</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5562</v>
+        <v>-0.5349</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7541</v>
+        <v>-3.7106</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9202</v>
+        <v>-4.2229</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3363</v>
+        <v>-1.9917</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4161</v>
+        <v>-2.2312</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8494</v>
+        <v>0.1201</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6916</v>
+        <v>0.8439</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1579</v>
+        <v>-0.7238</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7696</v>
+        <v>-4.343</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0279</v>
+        <v>-2.8356</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2582</v>
+        <v>-1.5074</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4641</v>
+        <v>0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0574</v>
+        <v>-1.0965</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2249</v>
+        <v>-0.655</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8325</v>
+        <v>-0.4416</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1314</v>
+        <v>0.4579</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8993</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7679</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8109</v>
+        <v>-5.0357</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4317</v>
+        <v>-2.7455</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3791</v>
+        <v>-2.2902</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2546</v>
+        <v>-0.4795</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2907</v>
+        <v>-0.6045</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0361</v>
+        <v>0.125</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9957</v>
+        <v>-7.593</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9696</v>
+        <v>-4.6558</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0261</v>
+        <v>-2.9372</v>
       </c>
       <c r="G23" t="n">
         <v>-6.296</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0837</v>
+        <v>-0.681</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2933</v>
+        <v>-0.2043</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
         <v>-5.3178</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.4107</v>
+        <v>-21.4108</v>
       </c>
       <c r="G24" t="n">
         <v>-18.7448</v>
@@ -2302,7 +2302,7 @@
         <v>4.5837</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.04490000000000061</v>
+        <v>-0.04490000000000016</v>
       </c>
       <c r="L24" t="n">
         <v>4.628799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>5.133400000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7537</v>
+        <v>-5.7536</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.9875</v>
+        <v>-5.9876</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2337</v>
+        <v>0.2336999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>1.8768</v>
